--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128626696</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128626699</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128626704</v>
       </c>
       <c r="B4" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128626706</v>
       </c>
       <c r="B5" t="n">
-        <v>78443</v>
+        <v>78447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626698</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626697</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>128626714</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128626713</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128626715</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128626705</v>
       </c>
       <c r="B15" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128626712</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>128626701</v>
       </c>
       <c r="B22" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128626695</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91408</v>
+        <v>91414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>128626704</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128626706</v>
       </c>
       <c r="B5" t="n">
-        <v>78447</v>
+        <v>78449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>128626714</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128626713</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128626715</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128626705</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91414</v>
+        <v>91416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128626712</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91416</v>
+        <v>91417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128626696</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128626699</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128626704</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128626706</v>
       </c>
       <c r="B5" t="n">
-        <v>78449</v>
+        <v>78476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626698</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626697</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>128626714</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128626713</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128626715</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128626705</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91417</v>
+        <v>91444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128626712</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>128626701</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128626695</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>128626704</v>
       </c>
       <c r="B4" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128626706</v>
       </c>
       <c r="B5" t="n">
-        <v>78476</v>
+        <v>78480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>128626714</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128626713</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128626715</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128626705</v>
       </c>
       <c r="B15" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91444</v>
+        <v>91449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128626712</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88899</v>
+        <v>88904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91513</v>
+        <v>91518</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91449</v>
+        <v>91454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91513</v>
+        <v>91518</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128626696</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128626699</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128626704</v>
       </c>
       <c r="B4" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128626706</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>78484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626698</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626697</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>128626714</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128626713</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128626715</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128626705</v>
       </c>
       <c r="B15" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128626712</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>128626701</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128626695</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128626696</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128626699</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128626704</v>
       </c>
       <c r="B4" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128626706</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>78389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626698</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626697</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>128626714</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128626713</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128626715</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128626705</v>
       </c>
       <c r="B15" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128626712</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>128626701</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128626695</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>128626704</v>
       </c>
       <c r="B4" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128626706</v>
       </c>
       <c r="B5" t="n">
-        <v>78389</v>
+        <v>78394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91511</v>
+        <v>91516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>128626714</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88915</v>
+        <v>88920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128626713</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91529</v>
+        <v>91534</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128626715</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128626705</v>
       </c>
       <c r="B15" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91465</v>
+        <v>91470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128626712</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91529</v>
+        <v>91534</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>128626704</v>
       </c>
       <c r="B4" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128626706</v>
       </c>
       <c r="B5" t="n">
-        <v>78394</v>
+        <v>78395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128626703</v>
       </c>
       <c r="B7" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128626707</v>
       </c>
       <c r="B9" t="n">
-        <v>91516</v>
+        <v>91522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>128626714</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128626716</v>
       </c>
       <c r="B11" t="n">
-        <v>88920</v>
+        <v>88926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128626713</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128626708</v>
       </c>
       <c r="B13" t="n">
-        <v>91534</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128626715</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128626705</v>
       </c>
       <c r="B15" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128626702</v>
       </c>
       <c r="B16" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128626712</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128626691</v>
       </c>
       <c r="B18" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128626693</v>
       </c>
       <c r="B19" t="n">
-        <v>92218</v>
+        <v>92226</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128626709</v>
       </c>
       <c r="B20" t="n">
-        <v>91534</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>128626710</v>
       </c>
       <c r="B21" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>128626692</v>
       </c>
       <c r="B24" t="n">
-        <v>92218</v>
+        <v>92226</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128626696</v>
+        <v>128626702</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398150</v>
+        <v>398155</v>
       </c>
       <c r="R2" t="n">
-        <v>7066318</v>
+        <v>7066195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128626699</v>
+        <v>128626706</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>78686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398083</v>
+        <v>398176</v>
       </c>
       <c r="R3" t="n">
-        <v>7066181</v>
+        <v>7066150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128626704</v>
+        <v>128626716</v>
       </c>
       <c r="B4" t="n">
-        <v>79194</v>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398149</v>
+        <v>398133</v>
       </c>
       <c r="R4" t="n">
-        <v>7066316</v>
+        <v>7066161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128626706</v>
+        <v>128626703</v>
       </c>
       <c r="B5" t="n">
-        <v>78395</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>498</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398176</v>
+        <v>398150</v>
       </c>
       <c r="R5" t="n">
-        <v>7066150</v>
+        <v>7066208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128626698</v>
+        <v>128626707</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398120</v>
+        <v>398082</v>
       </c>
       <c r="R6" t="n">
-        <v>7066219</v>
+        <v>7066193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128626703</v>
+        <v>128626691</v>
       </c>
       <c r="B7" t="n">
-        <v>91811</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398150</v>
+        <v>398153</v>
       </c>
       <c r="R7" t="n">
-        <v>7066208</v>
+        <v>7066207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,65 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128626697</v>
+        <v>128626708</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallsedet NNV, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398187</v>
+        <v>398105</v>
       </c>
       <c r="R8" t="n">
-        <v>7066247</v>
+        <v>7066171</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128626707</v>
+        <v>128626709</v>
       </c>
       <c r="B9" t="n">
-        <v>91522</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398082</v>
+        <v>398210</v>
       </c>
       <c r="R9" t="n">
-        <v>7066193</v>
+        <v>7066153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128626714</v>
+        <v>128626704</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398154</v>
+        <v>398149</v>
       </c>
       <c r="R10" t="n">
-        <v>7066151</v>
+        <v>7066316</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128626716</v>
+        <v>128626705</v>
       </c>
       <c r="B11" t="n">
-        <v>88926</v>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398133</v>
+        <v>398172</v>
       </c>
       <c r="R11" t="n">
-        <v>7066161</v>
+        <v>7066153</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128626713</v>
+        <v>128626692</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398128</v>
+        <v>398152</v>
       </c>
       <c r="R12" t="n">
-        <v>7066158</v>
+        <v>7066310</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1716,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128626708</v>
+        <v>128626693</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398105</v>
+        <v>398137</v>
       </c>
       <c r="R13" t="n">
-        <v>7066171</v>
+        <v>7066222</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,14 +1839,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128626715</v>
+        <v>128626712</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1919,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398173</v>
+        <v>398176</v>
       </c>
       <c r="R14" t="n">
-        <v>7066155</v>
+        <v>7066246</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128626705</v>
+        <v>128626713</v>
       </c>
       <c r="B15" t="n">
-        <v>79194</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398172</v>
+        <v>398128</v>
       </c>
       <c r="R15" t="n">
-        <v>7066153</v>
+        <v>7066158</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,6 +2012,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128626702</v>
+        <v>128626714</v>
       </c>
       <c r="B16" t="n">
-        <v>91476</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398155</v>
+        <v>398154</v>
       </c>
       <c r="R16" t="n">
-        <v>7066195</v>
+        <v>7066151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,6 +2114,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,14 +2145,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128626712</v>
+        <v>128626715</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2215,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398176</v>
+        <v>398173</v>
       </c>
       <c r="R17" t="n">
-        <v>7066246</v>
+        <v>7066155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128626691</v>
+        <v>128626695</v>
       </c>
       <c r="B18" t="n">
-        <v>91526</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398153</v>
+        <v>398220</v>
       </c>
       <c r="R18" t="n">
-        <v>7066207</v>
+        <v>7066310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2318,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128626693</v>
+        <v>128626696</v>
       </c>
       <c r="B19" t="n">
-        <v>92226</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398137</v>
+        <v>398150</v>
       </c>
       <c r="R19" t="n">
-        <v>7066222</v>
+        <v>7066318</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i högstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128626709</v>
+        <v>128626697</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,34 +2462,54 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallsedet NNV, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398210</v>
+        <v>398187</v>
       </c>
       <c r="R20" t="n">
-        <v>7066153</v>
+        <v>7066247</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,10 +2568,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128626710</v>
+        <v>128626698</v>
       </c>
       <c r="B21" t="n">
-        <v>91544</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2584,21 +2579,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2608,10 +2603,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398173</v>
+        <v>398120</v>
       </c>
       <c r="R21" t="n">
-        <v>7066156</v>
+        <v>7066219</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,6 +2639,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2670,10 +2670,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128626701</v>
+        <v>128626699</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398103</v>
+        <v>398083</v>
       </c>
       <c r="R22" t="n">
-        <v>7066163</v>
+        <v>7066181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128626695</v>
+        <v>128626701</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398220</v>
+        <v>398103</v>
       </c>
       <c r="R23" t="n">
-        <v>7066310</v>
+        <v>7066163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2871,103 +2871,6 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>128626692</v>
-      </c>
-      <c r="B24" t="n">
-        <v>92226</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Kallsedet NNV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>398152</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7066310</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36974-2025 artfynd.xlsx
+++ b/artfynd/A 36974-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626702</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626706</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626716</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626703</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626707</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626691</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626708</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626709</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626704</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626705</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626692</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626693</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626712</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626713</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626714</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626715</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626695</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2448,6 +2538,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626696</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2565,6 +2660,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626697</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2667,6 +2767,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626698</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626699</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2871,8 +2981,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626701</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>